--- a/data/misc_tra_data_temporary.xlsx
+++ b/data/misc_tra_data_temporary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E40FD308-CA66-481D-A1C4-085C18556C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{E40FD308-CA66-481D-A1C4-085C18556C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66304286-0F88-4D1F-9683-768F4A5C70D4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1AACB4F4-CCB1-4BFA-9412-C23C18D99322}"/>
+    <workbookView xWindow="37050" yWindow="3810" windowWidth="14400" windowHeight="7275" xr2:uid="{1AACB4F4-CCB1-4BFA-9412-C23C18D99322}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>diesel_rail</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>source</t>
+  </si>
+  <si>
+    <t>resid_marine_com</t>
+  </si>
+  <si>
+    <t>diesel_marine_com</t>
+  </si>
+  <si>
+    <t>diesel_marine_mil</t>
   </si>
 </sst>
 </file>
@@ -422,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCE022D-45C6-4B09-869B-E43B853AD9AF}">
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1260,6 +1269,318 @@
         <v>164.20000000000002</v>
       </c>
     </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="C9">
+        <v>66.7</v>
+      </c>
+      <c r="D9">
+        <v>68.2</v>
+      </c>
+      <c r="E9">
+        <v>62.2</v>
+      </c>
+      <c r="F9">
+        <v>50.5</v>
+      </c>
+      <c r="G9">
+        <v>46.3</v>
+      </c>
+      <c r="H9">
+        <v>50.9</v>
+      </c>
+      <c r="I9">
+        <v>67.2</v>
+      </c>
+      <c r="J9">
+        <v>71.8</v>
+      </c>
+      <c r="K9">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="L9">
+        <v>45.6</v>
+      </c>
+      <c r="M9">
+        <v>44.1</v>
+      </c>
+      <c r="N9">
+        <v>48.3</v>
+      </c>
+      <c r="O9">
+        <v>63.7</v>
+      </c>
+      <c r="P9">
+        <v>73.5</v>
+      </c>
+      <c r="Q9">
+        <v>65.3</v>
+      </c>
+      <c r="R9">
+        <v>57.5</v>
+      </c>
+      <c r="S9">
+        <v>61.6</v>
+      </c>
+      <c r="T9">
+        <v>60.6</v>
+      </c>
+      <c r="U9">
+        <v>51.9</v>
+      </c>
+      <c r="V9">
+        <v>62.1</v>
+      </c>
+      <c r="W9">
+        <v>52.9</v>
+      </c>
+      <c r="X9">
+        <v>52.8</v>
+      </c>
+      <c r="Y9">
+        <v>42.8</v>
+      </c>
+      <c r="Z9">
+        <v>45.9</v>
+      </c>
+      <c r="AA9">
+        <v>45.3</v>
+      </c>
+      <c r="AB9">
+        <v>43.5</v>
+      </c>
+      <c r="AC9">
+        <v>42.5</v>
+      </c>
+      <c r="AD9">
+        <v>39.6</v>
+      </c>
+      <c r="AE9">
+        <v>38.9</v>
+      </c>
+      <c r="AF9">
+        <v>41.1</v>
+      </c>
+      <c r="AG9">
+        <v>39.5</v>
+      </c>
+      <c r="AH9">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>715.7</v>
+      </c>
+      <c r="C10">
+        <v>801.51</v>
+      </c>
+      <c r="D10">
+        <v>669.84</v>
+      </c>
+      <c r="E10">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="F10">
+        <v>524.47</v>
+      </c>
+      <c r="G10">
+        <v>523.21</v>
+      </c>
+      <c r="H10">
+        <v>536.39</v>
+      </c>
+      <c r="I10">
+        <v>575.20000000000005</v>
+      </c>
+      <c r="J10">
+        <v>594.79999999999995</v>
+      </c>
+      <c r="K10">
+        <v>489.73</v>
+      </c>
+      <c r="L10">
+        <v>444.07</v>
+      </c>
+      <c r="M10">
+        <v>426.04</v>
+      </c>
+      <c r="N10">
+        <v>448.93</v>
+      </c>
+      <c r="O10">
+        <v>471.82</v>
+      </c>
+      <c r="P10">
+        <v>553.1</v>
+      </c>
+      <c r="Q10">
+        <v>581</v>
+      </c>
+      <c r="R10">
+        <v>599.37</v>
+      </c>
+      <c r="S10">
+        <v>607.54</v>
+      </c>
+      <c r="T10">
+        <v>654.61</v>
+      </c>
+      <c r="U10">
+        <v>604.78</v>
+      </c>
+      <c r="V10">
+        <v>619.80999999999995</v>
+      </c>
+      <c r="W10">
+        <v>518.37</v>
+      </c>
+      <c r="X10">
+        <v>459.46</v>
+      </c>
+      <c r="Y10">
+        <v>379.79</v>
+      </c>
+      <c r="Z10">
+        <v>369.18</v>
+      </c>
+      <c r="AA10">
+        <v>406.85</v>
+      </c>
+      <c r="AB10">
+        <v>450.68</v>
+      </c>
+      <c r="AC10">
+        <v>445.32</v>
+      </c>
+      <c r="AD10">
+        <v>417.57</v>
+      </c>
+      <c r="AE10">
+        <v>336.23</v>
+      </c>
+      <c r="AF10">
+        <v>293.99</v>
+      </c>
+      <c r="AG10">
+        <v>292.3</v>
+      </c>
+      <c r="AH10">
+        <v>325.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>85.55</v>
+      </c>
+      <c r="C11">
+        <v>82.58</v>
+      </c>
+      <c r="D11">
+        <v>77.77</v>
+      </c>
+      <c r="E11">
+        <v>84.46</v>
+      </c>
+      <c r="F11">
+        <v>70.7</v>
+      </c>
+      <c r="G11">
+        <v>79.44</v>
+      </c>
+      <c r="H11">
+        <v>63.26</v>
+      </c>
+      <c r="I11">
+        <v>58.34</v>
+      </c>
+      <c r="J11">
+        <v>87</v>
+      </c>
+      <c r="K11">
+        <v>42.71</v>
+      </c>
+      <c r="L11">
+        <v>40.25</v>
+      </c>
+      <c r="M11">
+        <v>28.3</v>
+      </c>
+      <c r="N11">
+        <v>34.26</v>
+      </c>
+      <c r="O11">
+        <v>40.229999999999997</v>
+      </c>
+      <c r="P11">
+        <v>70.05</v>
+      </c>
+      <c r="Q11">
+        <v>61.61</v>
+      </c>
+      <c r="R11">
+        <v>61.85</v>
+      </c>
+      <c r="S11">
+        <v>49.69</v>
+      </c>
+      <c r="T11">
+        <v>61.66</v>
+      </c>
+      <c r="U11">
+        <v>59.09</v>
+      </c>
+      <c r="V11">
+        <v>66.069999999999993</v>
+      </c>
+      <c r="W11">
+        <v>54.5</v>
+      </c>
+      <c r="X11">
+        <v>38.89</v>
+      </c>
+      <c r="Y11">
+        <v>32.659999999999997</v>
+      </c>
+      <c r="Z11">
+        <v>36.14</v>
+      </c>
+      <c r="AA11">
+        <v>68.239999999999995</v>
+      </c>
+      <c r="AB11">
+        <v>74.03</v>
+      </c>
+      <c r="AC11">
+        <v>78.790000000000006</v>
+      </c>
+      <c r="AD11">
+        <v>94.86</v>
+      </c>
+      <c r="AE11">
+        <v>97.34</v>
+      </c>
+      <c r="AF11">
+        <v>63.89</v>
+      </c>
+      <c r="AG11">
+        <v>60.62</v>
+      </c>
+      <c r="AH11">
+        <v>60.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
